--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N37_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>17.78857743979491</v>
       </c>
       <c r="E2" t="n">
-        <v>15.99457072302594</v>
+        <v>15.64502366632041</v>
       </c>
       <c r="F2" t="n">
-        <v>16.04784546463083</v>
+        <v>15.69255205867664</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>2.845558343376579</v>
       </c>
       <c r="E3" t="n">
-        <v>15.99457072302594</v>
+        <v>15.64502366632041</v>
       </c>
       <c r="F3" t="n">
-        <v>16.04784546463083</v>
+        <v>15.69255205867664</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>53.96894473830048</v>
       </c>
       <c r="E4" t="n">
-        <v>15.99457072302594</v>
+        <v>15.64502366632041</v>
       </c>
       <c r="F4" t="n">
-        <v>16.04784546463083</v>
+        <v>15.69255205867664</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>17.05412277947341</v>
       </c>
       <c r="E5" t="n">
-        <v>15.99457072302594</v>
+        <v>15.64502366632041</v>
       </c>
       <c r="F5" t="n">
-        <v>16.04784546463083</v>
+        <v>15.69255205867664</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.61764870021947</v>
+        <v>9.162773096262418</v>
       </c>
       <c r="D6" t="n">
-        <v>23.42806994741148</v>
+        <v>9.146670876226178</v>
       </c>
       <c r="E6" t="n">
-        <v>15.99457072302594</v>
+        <v>15.64502366632041</v>
       </c>
       <c r="F6" t="n">
-        <v>16.04784546463083</v>
+        <v>15.69255205867664</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.237734873816832</v>
+        <v>23.61764870021947</v>
       </c>
       <c r="D7" t="n">
-        <v>9.18117087260142</v>
+        <v>23.42806994741148</v>
       </c>
       <c r="E7" t="n">
-        <v>15.99457072302594</v>
+        <v>15.64502366632041</v>
       </c>
       <c r="F7" t="n">
-        <v>16.04784546463083</v>
+        <v>15.69255205867664</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,23 +672,55 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
+        <v>9.237734873816832</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9.18117087260142</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15.64502366632041</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15.69255205867664</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>T8387</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>W0075F0002T0006Z000C1N37.png</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="n">
         <v>36.66005527729953</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>36.55747460181046</v>
       </c>
-      <c r="E8" t="n">
-        <v>15.99457072302594</v>
-      </c>
-      <c r="F8" t="n">
-        <v>16.04784546463083</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="E9" t="n">
+        <v>15.64502366632041</v>
+      </c>
+      <c r="F9" t="n">
+        <v>15.69255205867664</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>T8387</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.29707352700855</v>
+        <v>2.810774448138889</v>
       </c>
       <c r="D2" t="n">
-        <v>17.78857743979491</v>
+        <v>2.890643833966673</v>
       </c>
       <c r="E2" t="n">
-        <v>15.64502366632041</v>
+        <v>2.542316345777066</v>
       </c>
       <c r="F2" t="n">
-        <v>15.69255205867664</v>
+        <v>2.550039709534954</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.240826463633482</v>
+        <v>0.5266343003404409</v>
       </c>
       <c r="D3" t="n">
-        <v>2.845558343376579</v>
+        <v>0.4624032307986941</v>
       </c>
       <c r="E3" t="n">
-        <v>15.64502366632041</v>
+        <v>2.542316345777066</v>
       </c>
       <c r="F3" t="n">
-        <v>15.69255205867664</v>
+        <v>2.550039709534954</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.90765269775599</v>
+        <v>8.759993563385349</v>
       </c>
       <c r="D4" t="n">
-        <v>53.96894473830048</v>
+        <v>8.769953519973829</v>
       </c>
       <c r="E4" t="n">
-        <v>15.64502366632041</v>
+        <v>2.542316345777066</v>
       </c>
       <c r="F4" t="n">
-        <v>15.69255205867664</v>
+        <v>2.550039709534954</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.98546661418446</v>
+        <v>2.760138324804975</v>
       </c>
       <c r="D5" t="n">
-        <v>17.05412277947341</v>
+        <v>2.771294951664429</v>
       </c>
       <c r="E5" t="n">
-        <v>15.64502366632041</v>
+        <v>2.542316345777066</v>
       </c>
       <c r="F5" t="n">
-        <v>15.69255205867664</v>
+        <v>2.550039709534954</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.162773096262418</v>
+        <v>1.488950628142643</v>
       </c>
       <c r="D6" t="n">
-        <v>9.146670876226178</v>
+        <v>1.486334017386754</v>
       </c>
       <c r="E6" t="n">
-        <v>15.64502366632041</v>
+        <v>2.542316345777066</v>
       </c>
       <c r="F6" t="n">
-        <v>15.69255205867664</v>
+        <v>2.550039709534954</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.61764870021947</v>
+        <v>3.837867913785665</v>
       </c>
       <c r="D7" t="n">
-        <v>23.42806994741148</v>
+        <v>3.807061366454366</v>
       </c>
       <c r="E7" t="n">
-        <v>15.64502366632041</v>
+        <v>2.542316345777066</v>
       </c>
       <c r="F7" t="n">
-        <v>15.69255205867664</v>
+        <v>2.550039709534954</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.237734873816832</v>
+        <v>1.501131916995235</v>
       </c>
       <c r="D8" t="n">
-        <v>9.18117087260142</v>
+        <v>1.491940266797731</v>
       </c>
       <c r="E8" t="n">
-        <v>15.64502366632041</v>
+        <v>2.542316345777066</v>
       </c>
       <c r="F8" t="n">
-        <v>15.69255205867664</v>
+        <v>2.550039709534954</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.66005527729953</v>
+        <v>5.957258982561174</v>
       </c>
       <c r="D9" t="n">
-        <v>36.55747460181046</v>
+        <v>5.9405896227942</v>
       </c>
       <c r="E9" t="n">
-        <v>15.64502366632041</v>
+        <v>2.542316345777066</v>
       </c>
       <c r="F9" t="n">
-        <v>15.69255205867664</v>
+        <v>2.550039709534954</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
